--- a/src/templates/pricing_spreadsheet.xlsx
+++ b/src/templates/pricing_spreadsheet.xlsx
@@ -8,20 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Joseph\Desktop\Code\MSSProposalAutomation\src\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72FFE77A-06E9-42C8-9EB2-29B5FBBC00B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64568B2E-1ED0-4694-9E07-A0E782AF1733}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="14914" activeTab="1" xr2:uid="{25869D54-3781-4886-8FF9-0A7E0B41E358}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="14914" activeTab="2" xr2:uid="{25869D54-3781-4886-8FF9-0A7E0B41E358}"/>
   </bookViews>
   <sheets>
     <sheet name="Customer Info" sheetId="9" r:id="rId1"/>
-    <sheet name="Pricing Calculator" sheetId="49" r:id="rId2"/>
-    <sheet name="Energy Usage" sheetId="7" r:id="rId3"/>
-    <sheet name="Financial Analysis" sheetId="8" r:id="rId4"/>
+    <sheet name="Edit Variables" sheetId="50" r:id="rId2"/>
+    <sheet name="Pricing Calculator" sheetId="49" r:id="rId3"/>
+    <sheet name="Energy Usage" sheetId="7" r:id="rId4"/>
+    <sheet name="Financial Analysis" sheetId="8" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Energy Usage'!$A$2:$Q$47</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'Financial Analysis'!#REF!</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Pricing Calculator'!$A$1:$M$106</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Energy Usage'!$A$2:$Q$47</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Financial Analysis'!#REF!</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Pricing Calculator'!$A$1:$M$106</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="214">
   <si>
     <t>AC Breaker</t>
   </si>
@@ -613,30 +614,9 @@
     <t>PCS</t>
   </si>
   <si>
-    <t>MSE410</t>
-  </si>
-  <si>
-    <t>IQ8AC</t>
-  </si>
-  <si>
     <t>{{JOB_NAME}}</t>
   </si>
   <si>
-    <t>{{CUSTOMER_NAME}}</t>
-  </si>
-  <si>
-    <t>{{CUSTOMER_ADDRESS_STREET}}</t>
-  </si>
-  <si>
-    <t>{{CUSTOMER_ADDRESS_CITY}}</t>
-  </si>
-  <si>
-    <t>{{CUSTOMER_ADDRESS_ZIP}}</t>
-  </si>
-  <si>
-    <t>{{CUSTOMER_EMAIL}}</t>
-  </si>
-  <si>
     <t>{{USAGE_JAN}}</t>
   </si>
   <si>
@@ -674,6 +654,36 @@
   </si>
   <si>
     <t>{{YEAR}}</t>
+  </si>
+  <si>
+    <t>{{CLIENT_NAME}}</t>
+  </si>
+  <si>
+    <t>{{CLIENT_ADDRESS_STREET}}</t>
+  </si>
+  <si>
+    <t>{{CLIENT_ADDRESS_CITY}}</t>
+  </si>
+  <si>
+    <t>{{CLIENT_ADDRESS_ZIP}}</t>
+  </si>
+  <si>
+    <t>{{CLIENT_EMAIL}}</t>
+  </si>
+  <si>
+    <t>{{PANEL_MODEL}}</t>
+  </si>
+  <si>
+    <t>{{INVERTER_MODEL}}</t>
+  </si>
+  <si>
+    <t>Value</t>
+  </si>
+  <si>
+    <t>Key</t>
+  </si>
+  <si>
+    <t>{{PANEL_COUNT}}</t>
   </si>
 </sst>
 </file>
@@ -3479,7 +3489,7 @@
         <v>153</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -3487,7 +3497,7 @@
         <v>147</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -3495,7 +3505,7 @@
         <v>148</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>194</v>
+        <v>205</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -3503,7 +3513,7 @@
         <v>149</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -3511,7 +3521,7 @@
         <v>150</v>
       </c>
       <c r="B5" s="76" t="s">
-        <v>196</v>
+        <v>207</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="15.9">
@@ -3533,7 +3543,7 @@
         <v>164</v>
       </c>
       <c r="B8" s="90" t="s">
-        <v>197</v>
+        <v>208</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -3596,6 +3606,24 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1710F80-8E9B-42D2-B4C6-C5445B098A6C}">
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr defaultRowHeight="12.45"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>211</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F117BFE-7259-4336-A083-7AFC1C274C1C}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -3717,11 +3745,10 @@
         <v>15</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="C10" s="119">
-        <f>D10*E10</f>
-        <v>30</v>
+        <v>209</v>
+      </c>
+      <c r="C10" s="119" t="s">
+        <v>213</v>
       </c>
       <c r="D10" s="120">
         <v>30</v>
@@ -3747,11 +3774,11 @@
         <v>18</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="C11" s="120">
+        <v>210</v>
+      </c>
+      <c r="C11" s="120" t="str">
         <f>C10</f>
-        <v>30</v>
+        <v>{{PANEL_COUNT}}</v>
       </c>
       <c r="D11" s="113" t="s">
         <v>160</v>
@@ -3760,9 +3787,9 @@
         <f>169+18</f>
         <v>187</v>
       </c>
-      <c r="H11" s="125">
+      <c r="H11" s="125" t="e">
         <f>G11/B18</f>
-        <v>1.4329501915708812E-2</v>
+        <v>#VALUE!</v>
       </c>
       <c r="I11" s="5" t="s">
         <v>133</v>
@@ -3780,13 +3807,13 @@
       </c>
       <c r="B12" s="2"/>
       <c r="C12" s="119"/>
-      <c r="G12" s="124">
+      <c r="G12" s="124" t="e">
         <f>65*C10+1450</f>
-        <v>3400</v>
-      </c>
-      <c r="H12" s="125">
+        <v>#VALUE!</v>
+      </c>
+      <c r="H12" s="125" t="e">
         <f>G12/B18</f>
-        <v>0.26053639846743293</v>
+        <v>#VALUE!</v>
       </c>
       <c r="I12" s="5" t="s">
         <v>134</v>
@@ -3878,9 +3905,9 @@
       <c r="A18" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="B18" s="10">
+      <c r="B18" s="10" t="e">
         <f>B14*C10</f>
-        <v>13050</v>
+        <v>#VALUE!</v>
       </c>
       <c r="L18" s="6"/>
       <c r="M18" s="6"/>
@@ -3890,9 +3917,9 @@
       <c r="A19" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="B19" s="10">
+      <c r="B19" s="10" t="e">
         <f>IF(B15*C10*B16&lt;B6, B15*C10*B16, "OVERCURRENT")</f>
-        <v>11772.404999999999</v>
+        <v>#VALUE!</v>
       </c>
       <c r="K19" s="4"/>
       <c r="L19" s="6"/>
@@ -3903,9 +3930,9 @@
       <c r="A20" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="B20" s="10">
+      <c r="B20" s="10" t="e">
         <f>B18*B17</f>
-        <v>10048.5</v>
+        <v>#VALUE!</v>
       </c>
       <c r="K20" s="4"/>
       <c r="M20" s="4"/>
@@ -3914,9 +3941,9 @@
       <c r="A21" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="B21" s="102">
+      <c r="B21" s="102" t="e">
         <f>B20*5.5*365/1000</f>
-        <v>20172.36375</v>
+        <v>#VALUE!</v>
       </c>
       <c r="C21" s="113" t="s">
         <v>108</v>
@@ -4002,17 +4029,17 @@
       <c r="B28" s="9">
         <v>1</v>
       </c>
-      <c r="C28" s="133">
+      <c r="C28" s="133" t="e">
         <f>((B14*C10*G10)+G11*C11+G12)*1.07875</f>
-        <v>16054.496875000001</v>
-      </c>
-      <c r="D28" s="113">
+        <v>#VALUE!</v>
+      </c>
+      <c r="D28" s="113" t="e">
         <f>B28*C28</f>
-        <v>16054.496875000001</v>
-      </c>
-      <c r="E28" s="134">
+        <v>#VALUE!</v>
+      </c>
+      <c r="E28" s="134" t="e">
         <f>D28/$B$18</f>
-        <v>1.2302296455938697</v>
+        <v>#VALUE!</v>
       </c>
       <c r="G28" s="104" t="s">
         <v>102</v>
@@ -4039,9 +4066,9 @@
         <f>B29*C29</f>
         <v>0</v>
       </c>
-      <c r="E29" s="134">
+      <c r="E29" s="134" t="e">
         <f>D29/$B$18</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="G29" s="104" t="s">
         <v>102</v>
@@ -4068,9 +4095,9 @@
         <f>B30*C30</f>
         <v>2002.5</v>
       </c>
-      <c r="E30" s="137">
+      <c r="E30" s="137" t="e">
         <f>D30/$B$18</f>
-        <v>0.15344827586206897</v>
+        <v>#VALUE!</v>
       </c>
       <c r="G30" s="104" t="s">
         <v>1</v>
@@ -4089,13 +4116,13 @@
       </c>
       <c r="B31" s="18"/>
       <c r="C31" s="138"/>
-      <c r="D31" s="139">
+      <c r="D31" s="139" t="e">
         <f>SUM(D28:D30)</f>
-        <v>18056.996875000001</v>
-      </c>
-      <c r="E31" s="140">
+        <v>#VALUE!</v>
+      </c>
+      <c r="E31" s="140" t="e">
         <f>D31/$B$18</f>
-        <v>1.3836779214559387</v>
+        <v>#VALUE!</v>
       </c>
       <c r="G31" s="20"/>
       <c r="I31" s="19"/>
@@ -4143,9 +4170,9 @@
         <f>B34*C34</f>
         <v>0</v>
       </c>
-      <c r="E34" s="134">
+      <c r="E34" s="134" t="e">
         <f>D34/$B$18</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="G34" s="104" t="s">
         <v>102</v>
@@ -4169,9 +4196,9 @@
         <f>B35*C35</f>
         <v>0</v>
       </c>
-      <c r="E35" s="134">
+      <c r="E35" s="134" t="e">
         <f>D35/$B$18</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="G35" s="104" t="s">
         <v>102</v>
@@ -4195,9 +4222,9 @@
         <f>B36*C36</f>
         <v>0</v>
       </c>
-      <c r="E36" s="134">
+      <c r="E36" s="134" t="e">
         <f>D36/$B$18</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="G36" s="104" t="s">
         <v>102</v>
@@ -4222,9 +4249,9 @@
         <f>B37*C37</f>
         <v>0</v>
       </c>
-      <c r="E37" s="137">
+      <c r="E37" s="137" t="e">
         <f>D37/$B$18</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="G37" s="104" t="s">
         <v>1</v>
@@ -4245,9 +4272,9 @@
         <f>SUM(D34:D37)</f>
         <v>0</v>
       </c>
-      <c r="E38" s="140">
+      <c r="E38" s="140" t="e">
         <f>D38/$B$18</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="G38" s="20"/>
       <c r="H38" s="19"/>
@@ -4289,9 +4316,9 @@
         <f>B41*C41</f>
         <v>0</v>
       </c>
-      <c r="E41" s="134">
+      <c r="E41" s="134" t="e">
         <f t="shared" ref="E41:E46" si="0">D41/$B$18</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="G41" s="104" t="s">
         <v>102</v>
@@ -4311,9 +4338,9 @@
         <f>B42*C42</f>
         <v>0</v>
       </c>
-      <c r="E42" s="134">
+      <c r="E42" s="134" t="e">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="G42" s="104" t="s">
         <v>1</v>
@@ -4333,9 +4360,9 @@
         <f>B43*C43</f>
         <v>70</v>
       </c>
-      <c r="E43" s="134">
+      <c r="E43" s="134" t="e">
         <f t="shared" si="0"/>
-        <v>5.3639846743295016E-3</v>
+        <v>#VALUE!</v>
       </c>
       <c r="G43" s="104" t="s">
         <v>102</v>
@@ -4360,9 +4387,9 @@
         <f>B44*C44</f>
         <v>200</v>
       </c>
-      <c r="E44" s="134">
+      <c r="E44" s="134" t="e">
         <f t="shared" si="0"/>
-        <v>1.532567049808429E-2</v>
+        <v>#VALUE!</v>
       </c>
       <c r="G44" s="104" t="s">
         <v>102</v>
@@ -4382,9 +4409,9 @@
         <f>B45*C45</f>
         <v>0</v>
       </c>
-      <c r="E45" s="137">
+      <c r="E45" s="137" t="e">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="G45" s="104" t="s">
         <v>1</v>
@@ -4401,9 +4428,9 @@
         <f>SUM(D41:D45)</f>
         <v>270</v>
       </c>
-      <c r="E46" s="140">
+      <c r="E46" s="140" t="e">
         <f t="shared" si="0"/>
-        <v>2.0689655172413793E-2</v>
+        <v>#VALUE!</v>
       </c>
       <c r="G46" s="20"/>
       <c r="L46" s="5"/>
@@ -4438,9 +4465,9 @@
         <f>B49*C49</f>
         <v>1600</v>
       </c>
-      <c r="E49" s="134">
+      <c r="E49" s="134" t="e">
         <f>D49/$B$18</f>
-        <v>0.12260536398467432</v>
+        <v>#VALUE!</v>
       </c>
       <c r="G49" s="104" t="s">
         <v>102</v>
@@ -4469,9 +4496,9 @@
         <f>B50*C50</f>
         <v>100</v>
       </c>
-      <c r="E50" s="134">
+      <c r="E50" s="134" t="e">
         <f>D50/$B$18</f>
-        <v>7.6628352490421452E-3</v>
+        <v>#VALUE!</v>
       </c>
       <c r="G50" s="104" t="s">
         <v>102</v>
@@ -4491,9 +4518,9 @@
         <f>B51*C51</f>
         <v>0</v>
       </c>
-      <c r="E51" s="137">
+      <c r="E51" s="137" t="e">
         <f>D51/$B$18</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="G51" s="104" t="s">
         <v>1</v>
@@ -4510,9 +4537,9 @@
         <f>SUM(D49:D51)</f>
         <v>1700</v>
       </c>
-      <c r="E52" s="140">
+      <c r="E52" s="140" t="e">
         <f>D52/$B$18</f>
-        <v>0.13026819923371646</v>
+        <v>#VALUE!</v>
       </c>
       <c r="G52" s="20"/>
       <c r="L52" s="5"/>
@@ -4547,9 +4574,9 @@
         <f t="shared" ref="D55:D62" si="1">B55*C55</f>
         <v>150</v>
       </c>
-      <c r="E55" s="134">
+      <c r="E55" s="134" t="e">
         <f t="shared" ref="E55:E63" si="2">D55/$B$18</f>
-        <v>1.1494252873563218E-2</v>
+        <v>#VALUE!</v>
       </c>
       <c r="G55" s="104" t="s">
         <v>1</v>
@@ -4569,9 +4596,9 @@
         <f t="shared" si="1"/>
         <v>550</v>
       </c>
-      <c r="E56" s="134">
+      <c r="E56" s="134" t="e">
         <f t="shared" si="2"/>
-        <v>4.2145593869731802E-2</v>
+        <v>#VALUE!</v>
       </c>
       <c r="G56" s="104" t="s">
         <v>102</v>
@@ -4591,9 +4618,9 @@
         <f t="shared" si="1"/>
         <v>900</v>
       </c>
-      <c r="E57" s="134">
+      <c r="E57" s="134" t="e">
         <f t="shared" si="2"/>
-        <v>6.8965517241379309E-2</v>
+        <v>#VALUE!</v>
       </c>
       <c r="G57" s="104" t="s">
         <v>102</v>
@@ -4616,9 +4643,9 @@
         <f t="shared" si="1"/>
         <v>75</v>
       </c>
-      <c r="E58" s="134">
+      <c r="E58" s="134" t="e">
         <f t="shared" si="2"/>
-        <v>5.7471264367816091E-3</v>
+        <v>#VALUE!</v>
       </c>
       <c r="G58" s="104" t="s">
         <v>1</v>
@@ -4639,9 +4666,9 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="E59" s="134">
+      <c r="E59" s="134" t="e">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="G59" s="104" t="s">
         <v>102</v>
@@ -4661,9 +4688,9 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="E60" s="134">
+      <c r="E60" s="134" t="e">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="G60" s="104" t="s">
         <v>102</v>
@@ -4687,9 +4714,9 @@
         <f t="shared" si="1"/>
         <v>200</v>
       </c>
-      <c r="E61" s="134">
+      <c r="E61" s="134" t="e">
         <f t="shared" si="2"/>
-        <v>1.532567049808429E-2</v>
+        <v>#VALUE!</v>
       </c>
       <c r="G61" s="104" t="s">
         <v>102</v>
@@ -4712,9 +4739,9 @@
         <f t="shared" si="1"/>
         <v>50</v>
       </c>
-      <c r="E62" s="137">
+      <c r="E62" s="137" t="e">
         <f t="shared" si="2"/>
-        <v>3.8314176245210726E-3</v>
+        <v>#VALUE!</v>
       </c>
       <c r="G62" s="104" t="s">
         <v>1</v>
@@ -4734,9 +4761,9 @@
         <f>SUM(D55:D62)</f>
         <v>1925</v>
       </c>
-      <c r="E63" s="140">
+      <c r="E63" s="140" t="e">
         <f t="shared" si="2"/>
-        <v>0.1475095785440613</v>
+        <v>#VALUE!</v>
       </c>
       <c r="G63" s="20"/>
       <c r="L63" s="5"/>
@@ -4762,9 +4789,9 @@
       <c r="D66" s="123">
         <v>0</v>
       </c>
-      <c r="E66" s="141">
+      <c r="E66" s="141" t="e">
         <f t="shared" ref="E66:E71" si="3">D66/$B$18</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="G66" s="104" t="s">
         <v>102</v>
@@ -4791,9 +4818,9 @@
       <c r="D68" s="123">
         <v>0</v>
       </c>
-      <c r="E68" s="141">
+      <c r="E68" s="141" t="e">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="G68" s="104" t="s">
         <v>1</v>
@@ -4809,9 +4836,9 @@
       <c r="D69" s="123">
         <v>50</v>
       </c>
-      <c r="E69" s="141">
+      <c r="E69" s="141" t="e">
         <f t="shared" si="3"/>
-        <v>3.8314176245210726E-3</v>
+        <v>#VALUE!</v>
       </c>
       <c r="G69" s="104" t="s">
         <v>102</v>
@@ -4826,9 +4853,9 @@
         <v>27</v>
       </c>
       <c r="D70" s="143"/>
-      <c r="E70" s="144">
+      <c r="E70" s="144" t="e">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="G70" s="104" t="s">
         <v>1</v>
@@ -4846,9 +4873,9 @@
         <f>SUM(D66:D70)</f>
         <v>1050</v>
       </c>
-      <c r="E71" s="145">
+      <c r="E71" s="145" t="e">
         <f t="shared" si="3"/>
-        <v>8.0459770114942528E-2</v>
+        <v>#VALUE!</v>
       </c>
       <c r="M71" s="1"/>
       <c r="N71" s="1"/>
@@ -4873,13 +4900,13 @@
       </c>
       <c r="B74" s="2"/>
       <c r="C74" s="147"/>
-      <c r="D74" s="147">
+      <c r="D74" s="147" t="e">
         <f>SUM(D28,D29,D34,D35,D36,D41,D43,D44,D49,D50,D56,D57,D59,D60,D61,D66,D67, D69)</f>
-        <v>20724.496875000001</v>
-      </c>
-      <c r="E74" s="148">
+        <v>#VALUE!</v>
+      </c>
+      <c r="E74" s="148" t="e">
         <f>D74/$B$18</f>
-        <v>1.5880840517241379</v>
+        <v>#VALUE!</v>
       </c>
       <c r="J74" s="106"/>
       <c r="K74" s="107"/>
@@ -4898,9 +4925,9 @@
         <f>SUM(D30,D37,D42,D45,D51,D55,D58,D62,D68, D70)</f>
         <v>2277.5</v>
       </c>
-      <c r="E75" s="148">
+      <c r="E75" s="148" t="e">
         <f>D75/$B$18</f>
-        <v>0.17452107279693488</v>
+        <v>#VALUE!</v>
       </c>
       <c r="F75" s="5">
         <f>SUM(B30,B37,B42,B45,B51,B55,B58,B62)</f>
@@ -4944,9 +4971,9 @@
         <f>D88*C77</f>
         <v>0</v>
       </c>
-      <c r="E77" s="134">
+      <c r="E77" s="134" t="e">
         <f t="shared" ref="E77:E82" si="4">D77/$B$18</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="J77" s="149"/>
       <c r="L77" s="152"/>
@@ -4958,9 +4985,9 @@
       <c r="D78" s="123">
         <v>250</v>
       </c>
-      <c r="E78" s="141">
+      <c r="E78" s="141" t="e">
         <f t="shared" si="4"/>
-        <v>1.9157088122605363E-2</v>
+        <v>#VALUE!</v>
       </c>
       <c r="G78" s="105"/>
       <c r="J78" s="12"/>
@@ -4973,13 +5000,13 @@
       <c r="C79" s="151">
         <v>0</v>
       </c>
-      <c r="D79" s="113">
+      <c r="D79" s="113" t="e">
         <f>D98*C79</f>
-        <v>0</v>
-      </c>
-      <c r="E79" s="134">
+        <v>#VALUE!</v>
+      </c>
+      <c r="E79" s="134" t="e">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="J79" s="12"/>
       <c r="L79" s="1"/>
@@ -4991,13 +5018,13 @@
       <c r="C80" s="153">
         <v>0</v>
       </c>
-      <c r="D80" s="113">
+      <c r="D80" s="113" t="e">
         <f>C80*B19</f>
-        <v>0</v>
-      </c>
-      <c r="E80" s="134">
+        <v>#VALUE!</v>
+      </c>
+      <c r="E80" s="134" t="e">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="G80" s="12"/>
       <c r="J80" s="12"/>
@@ -5009,9 +5036,9 @@
       <c r="D81" s="154">
         <v>1800</v>
       </c>
-      <c r="E81" s="155">
+      <c r="E81" s="155" t="e">
         <f t="shared" si="4"/>
-        <v>0.13793103448275862</v>
+        <v>#VALUE!</v>
       </c>
       <c r="J81" s="12"/>
     </row>
@@ -5022,13 +5049,13 @@
       </c>
       <c r="B82" s="2"/>
       <c r="C82" s="147"/>
-      <c r="D82" s="156">
+      <c r="D82" s="156" t="e">
         <f>SUM(D74:D81)</f>
-        <v>25051.996875000001</v>
-      </c>
-      <c r="E82" s="157">
+        <v>#VALUE!</v>
+      </c>
+      <c r="E82" s="157" t="e">
         <f t="shared" si="4"/>
-        <v>1.9196932471264367</v>
+        <v>#VALUE!</v>
       </c>
       <c r="H82" s="12"/>
       <c r="J82" s="12"/>
@@ -5038,9 +5065,9 @@
       <c r="C83" s="158" t="s">
         <v>66</v>
       </c>
-      <c r="D83" s="147">
+      <c r="D83" s="147" t="e">
         <f>D82/B18</f>
-        <v>1.9196932471264367</v>
+        <v>#VALUE!</v>
       </c>
       <c r="E83" s="147"/>
       <c r="J83" s="56"/>
@@ -5051,9 +5078,9 @@
       <c r="C84" s="158" t="s">
         <v>67</v>
       </c>
-      <c r="D84" s="113">
+      <c r="D84" s="113" t="e">
         <f>D82/B19</f>
-        <v>2.1280271002399256</v>
+        <v>#VALUE!</v>
       </c>
       <c r="J84" s="12"/>
       <c r="L84" s="1"/>
@@ -5080,30 +5107,30 @@
       <c r="B88" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="C88" s="159">
+      <c r="C88" s="159" t="e">
         <f>D88/B18</f>
-        <v>2.596168582375479</v>
+        <v>#VALUE!</v>
       </c>
       <c r="D88" s="160">
         <v>33880</v>
       </c>
       <c r="H88" s="37"/>
-      <c r="I88" s="161">
+      <c r="I88" s="161" t="e">
         <f>J88/D82</f>
-        <v>0.35238720366477766</v>
-      </c>
-      <c r="J88" s="162">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J88" s="162" t="e">
         <f>D88-D82</f>
-        <v>8828.0031249999993</v>
+        <v>#VALUE!</v>
       </c>
       <c r="K88" s="25"/>
-      <c r="L88" s="163">
+      <c r="L88" s="163" t="e">
         <f>J88/D88/2</f>
-        <v>0.1302833991292798</v>
-      </c>
-      <c r="M88" s="12">
+        <v>#VALUE!</v>
+      </c>
+      <c r="M88" s="12" t="e">
         <f>D82/(1/0.285)</f>
-        <v>7139.8191093750002</v>
+        <v>#VALUE!</v>
       </c>
       <c r="N88" s="111" t="s">
         <v>188</v>
@@ -5115,9 +5142,9 @@
       </c>
       <c r="H89" s="26"/>
       <c r="I89" s="27"/>
-      <c r="J89" s="12">
+      <c r="J89" s="12" t="e">
         <f>J88/B19</f>
-        <v>0.749889519176413</v>
+        <v>#VALUE!</v>
       </c>
       <c r="K89" s="22" t="s">
         <v>69</v>
@@ -5127,9 +5154,9 @@
       <c r="B90" s="13"/>
       <c r="H90" s="26"/>
       <c r="I90" s="27"/>
-      <c r="J90" s="12">
+      <c r="J90" s="12" t="e">
         <f>J88/B18</f>
-        <v>0.67647533524904213</v>
+        <v>#VALUE!</v>
       </c>
       <c r="K90" s="22" t="s">
         <v>66</v>
@@ -5151,18 +5178,18 @@
       <c r="C92" s="159">
         <v>5.45</v>
       </c>
-      <c r="D92" s="113">
+      <c r="D92" s="113" t="e">
         <f>C92*B19</f>
-        <v>64159.607249999994</v>
+        <v>#VALUE!</v>
       </c>
       <c r="H92" s="38"/>
-      <c r="I92" s="164">
+      <c r="I92" s="164" t="e">
         <f>J92/D82</f>
-        <v>1.5610576103027711</v>
-      </c>
-      <c r="J92" s="165">
+        <v>#VALUE!</v>
+      </c>
+      <c r="J92" s="165" t="e">
         <f>D92-D82</f>
-        <v>39107.610374999989</v>
+        <v>#VALUE!</v>
       </c>
       <c r="K92" s="22"/>
     </row>
@@ -5172,9 +5199,9 @@
       </c>
       <c r="H93" s="29"/>
       <c r="I93" s="166"/>
-      <c r="J93" s="12">
+      <c r="J93" s="12" t="e">
         <f>J92/B19</f>
-        <v>3.3219728997600741</v>
+        <v>#VALUE!</v>
       </c>
       <c r="K93" s="22" t="s">
         <v>69</v>
@@ -5183,9 +5210,9 @@
     <row r="94" spans="1:14">
       <c r="H94" s="30"/>
       <c r="I94" s="8"/>
-      <c r="J94" s="31">
+      <c r="J94" s="31" t="e">
         <f>J92/B18</f>
-        <v>2.9967517528735623</v>
+        <v>#VALUE!</v>
       </c>
       <c r="K94" s="24" t="s">
         <v>66</v>
@@ -5213,9 +5240,9 @@
       <c r="C97" s="151">
         <v>0</v>
       </c>
-      <c r="D97" s="113">
+      <c r="D97" s="113" t="e">
         <f>-J99*C97</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="H97" s="35" t="s">
         <v>72</v>
@@ -5223,13 +5250,13 @@
       <c r="I97" s="154">
         <v>0</v>
       </c>
-      <c r="J97" s="152">
+      <c r="J97" s="152" t="e">
         <f>I97*$B$19</f>
-        <v>0</v>
-      </c>
-      <c r="K97" s="168">
+        <v>#VALUE!</v>
+      </c>
+      <c r="K97" s="168" t="e">
         <f>J97/D88</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="L97" s="22" t="s">
         <v>38</v>
@@ -5239,21 +5266,21 @@
       <c r="C98" s="158" t="s">
         <v>39</v>
       </c>
-      <c r="D98" s="169">
+      <c r="D98" s="169" t="e">
         <f>D88-D97</f>
-        <v>33880</v>
+        <v>#VALUE!</v>
       </c>
       <c r="H98" s="35" t="s">
         <v>73</v>
       </c>
       <c r="I98" s="154"/>
-      <c r="J98" s="152">
+      <c r="J98" s="152" t="e">
         <f>I98*$B$19</f>
-        <v>0</v>
-      </c>
-      <c r="K98" s="168">
+        <v>#VALUE!</v>
+      </c>
+      <c r="K98" s="168" t="e">
         <f>J98/D88</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="L98" s="22" t="s">
         <v>38</v>
@@ -5265,13 +5292,13 @@
         <v>74</v>
       </c>
       <c r="I99" s="143"/>
-      <c r="J99" s="136">
+      <c r="J99" s="136" t="e">
         <f>I99*$B$19</f>
-        <v>0</v>
-      </c>
-      <c r="K99" s="170">
+        <v>#VALUE!</v>
+      </c>
+      <c r="K99" s="170" t="e">
         <f>J99/D88</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
       <c r="L99" s="24" t="s">
         <v>38</v>
@@ -5284,9 +5311,9 @@
       <c r="C100" s="15">
         <v>0</v>
       </c>
-      <c r="D100" s="113">
+      <c r="D100" s="113" t="e">
         <f>-C100*D98</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="101" spans="1:12">
@@ -5305,18 +5332,18 @@
       <c r="C103" s="113" t="s">
         <v>36</v>
       </c>
-      <c r="D103" s="113">
+      <c r="D103" s="113" t="e">
         <f>D97+D100+D101</f>
-        <v>0</v>
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="104" spans="1:12" ht="12.9" thickBot="1">
       <c r="C104" s="158" t="s">
         <v>37</v>
       </c>
-      <c r="D104" s="160">
+      <c r="D104" s="160" t="e">
         <f>D88+D103</f>
-        <v>33880</v>
+        <v>#VALUE!</v>
       </c>
       <c r="I104" s="171"/>
     </row>
@@ -5324,9 +5351,9 @@
       <c r="C105" s="158" t="s">
         <v>66</v>
       </c>
-      <c r="D105" s="113">
+      <c r="D105" s="113" t="e">
         <f>D104/B18</f>
-        <v>2.596168582375479</v>
+        <v>#VALUE!</v>
       </c>
       <c r="I105" s="171"/>
     </row>
@@ -5334,9 +5361,9 @@
       <c r="C106" s="158" t="s">
         <v>67</v>
       </c>
-      <c r="D106" s="113">
+      <c r="D106" s="113" t="e">
         <f>D104/B19</f>
-        <v>2.8779166194163386</v>
+        <v>#VALUE!</v>
       </c>
       <c r="I106" s="171"/>
     </row>
@@ -5362,7 +5389,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A37A59E6-E70A-4883-848E-CE690CF9E76A}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -6056,7 +6083,7 @@
         <v>169</v>
       </c>
       <c r="K28" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="L28" s="110"/>
       <c r="M28" s="98"/>
@@ -6087,7 +6114,7 @@
         <v>170</v>
       </c>
       <c r="K29" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="L29" s="110"/>
       <c r="M29" s="100"/>
@@ -6119,7 +6146,7 @@
         <v>171</v>
       </c>
       <c r="K30" t="s">
-        <v>200</v>
+        <v>193</v>
       </c>
       <c r="L30" s="110"/>
       <c r="M30" s="99"/>
@@ -6151,7 +6178,7 @@
         <v>172</v>
       </c>
       <c r="K31" t="s">
-        <v>201</v>
+        <v>194</v>
       </c>
       <c r="L31" s="110"/>
       <c r="M31" s="99"/>
@@ -6183,7 +6210,7 @@
         <v>84</v>
       </c>
       <c r="K32" t="s">
-        <v>202</v>
+        <v>195</v>
       </c>
       <c r="L32" s="110"/>
       <c r="M32" s="99"/>
@@ -6219,7 +6246,7 @@
         <v>173</v>
       </c>
       <c r="K33" t="s">
-        <v>203</v>
+        <v>196</v>
       </c>
       <c r="L33" s="110"/>
       <c r="M33" s="99"/>
@@ -6255,7 +6282,7 @@
         <v>174</v>
       </c>
       <c r="K34" t="s">
-        <v>204</v>
+        <v>197</v>
       </c>
       <c r="L34" s="110"/>
       <c r="M34" s="99"/>
@@ -6293,7 +6320,7 @@
         <v>175</v>
       </c>
       <c r="K35" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="L35" s="110"/>
       <c r="M35" s="99"/>
@@ -6331,7 +6358,7 @@
         <v>176</v>
       </c>
       <c r="K36" t="s">
-        <v>206</v>
+        <v>199</v>
       </c>
       <c r="L36" s="110"/>
       <c r="M36" s="99"/>
@@ -6369,7 +6396,7 @@
         <v>177</v>
       </c>
       <c r="K37" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="L37" s="110"/>
       <c r="M37" s="99"/>
@@ -6403,7 +6430,7 @@
         <v>178</v>
       </c>
       <c r="K38" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="L38" s="110"/>
       <c r="M38" s="99"/>
@@ -6437,7 +6464,7 @@
         <v>179</v>
       </c>
       <c r="K39" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
       <c r="L39" s="110"/>
       <c r="M39" s="99"/>
@@ -6633,7 +6660,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE350512-1622-446F-B868-8FF83874E81A}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -6713,7 +6740,7 @@
         <v>121</v>
       </c>
       <c r="H9" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
     </row>
     <row r="10" spans="1:10">

--- a/src/templates/pricing_spreadsheet.xlsx
+++ b/src/templates/pricing_spreadsheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Joseph\Desktop\Code\MSSProposalAutomation\src\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64568B2E-1ED0-4694-9E07-A0E782AF1733}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99567BE3-290F-49F4-828B-B7BBA1332BB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="14914" activeTab="2" xr2:uid="{25869D54-3781-4886-8FF9-0A7E0B41E358}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="14914" activeTab="1" xr2:uid="{25869D54-3781-4886-8FF9-0A7E0B41E358}"/>
   </bookViews>
   <sheets>
     <sheet name="Customer Info" sheetId="9" r:id="rId1"/>
@@ -1460,7 +1460,18 @@
     <cellStyle name="Percent 4 2" xfId="18" xr:uid="{7BAA56FC-0622-437A-8994-4834844CD280}"/>
     <cellStyle name="Percent 5" xfId="19" xr:uid="{C4D463B5-7253-4A7F-9A47-ED375D1C093D}"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <strike val="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor theme="5"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -3609,6 +3620,10 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1710F80-8E9B-42D2-B4C6-C5445B098A6C}">
   <dimension ref="A1:B1"/>
   <sheetFormatPr defaultRowHeight="12.45"/>
+  <cols>
+    <col min="1" max="1" width="40.69140625" customWidth="1"/>
+    <col min="2" max="2" width="20.69140625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
@@ -3619,6 +3634,11 @@
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="B1:B1048576">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>A1=""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>

--- a/src/templates/pricing_spreadsheet.xlsx
+++ b/src/templates/pricing_spreadsheet.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Joseph\Desktop\Code\MSSProposalAutomation\src\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99567BE3-290F-49F4-828B-B7BBA1332BB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4A9B45B-0389-4424-9CCD-1A78EE6ED479}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="14914" activeTab="1" xr2:uid="{25869D54-3781-4886-8FF9-0A7E0B41E358}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="219">
   <si>
     <t>AC Breaker</t>
   </si>
@@ -684,6 +684,21 @@
   </si>
   <si>
     <t>{{PANEL_COUNT}}</t>
+  </si>
+  <si>
+    <t>Utility</t>
+  </si>
+  <si>
+    <t>Tree Trimming Required?</t>
+  </si>
+  <si>
+    <t>Loan Term</t>
+  </si>
+  <si>
+    <t>Interest Rate</t>
+  </si>
+  <si>
+    <t>Monthly Payment</t>
   </si>
 </sst>
 </file>
@@ -1061,7 +1076,7 @@
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="27" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="175">
+  <cellXfs count="180">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1428,6 +1443,13 @@
     </xf>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="1" xfId="18" applyFont="1" applyBorder="1"/>
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" xfId="18" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
     <xf numFmtId="8" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1436,6 +1458,16 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="0" borderId="0" xfId="10" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" xfId="10" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="10" fontId="6" fillId="0" borderId="0" xfId="14" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" xfId="6" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="20">
@@ -3201,6 +3233,23 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
+<FeaturePropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
+  <bag type="Checkbox"/>
+  <bag type="XFControls">
+    <bagId k="CellControl">0</bagId>
+  </bag>
+  <bag type="XFComplement">
+    <bagId k="XFControls">1</bagId>
+  </bag>
+  <bag type="XFComplements" extRef="XFComplementsMapperExtRef">
+    <a k="MappedFeaturePropertyBags">
+      <bagId>2</bagId>
+    </a>
+  </bag>
+</FeaturePropertyBags>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
@@ -3568,8 +3617,9 @@
         <v>156</v>
       </c>
       <c r="B10" s="82"/>
-      <c r="C10" s="5" t="s">
-        <v>73</v>
+      <c r="C10" s="5" t="str">
+        <f>'Edit Variables'!B2</f>
+        <v>MID</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -3618,7 +3668,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1710F80-8E9B-42D2-B4C6-C5445B098A6C}">
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="12.45"/>
   <cols>
     <col min="1" max="1" width="40.69140625" customWidth="1"/>
@@ -3633,12 +3683,33 @@
         <v>211</v>
       </c>
     </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>215</v>
+      </c>
+      <c r="B3" s="172" t="b">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="B1:B1048576">
     <cfRule type="expression" dxfId="0" priority="1">
-      <formula>A1=""</formula>
+      <formula>B1=""</formula>
     </cfRule>
   </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2" xr:uid="{60B8E31B-39B7-4944-9BC6-9AF1B77C6E94}">
+      <formula1>"MID, PG&amp;E"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -5391,12 +5462,44 @@
       <c r="I107" s="171"/>
     </row>
     <row r="108" spans="1:12">
+      <c r="C108" s="158" t="s">
+        <v>216</v>
+      </c>
+      <c r="D108" s="176">
+        <v>12</v>
+      </c>
       <c r="K108" s="171"/>
     </row>
     <row r="109" spans="1:12">
-      <c r="C109" s="158"/>
-    </row>
-    <row r="125" spans="9:9">
+      <c r="C109" s="158" t="s">
+        <v>217</v>
+      </c>
+      <c r="D109" s="178">
+        <v>6.7400000000000002E-2</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12">
+      <c r="C110" s="177" t="s">
+        <v>218</v>
+      </c>
+      <c r="D110" s="179">
+        <f>D88*(((D109/12)*(1+(D109/12))^(D108*12))/(((1+(D109/12))^(D108*12))-1))</f>
+        <v>343.73752351267893</v>
+      </c>
+    </row>
+    <row r="111" spans="1:12">
+      <c r="C111" s="158"/>
+      <c r="D111" s="158"/>
+    </row>
+    <row r="112" spans="1:12">
+      <c r="C112" s="158"/>
+      <c r="D112" s="158"/>
+    </row>
+    <row r="113" spans="3:9">
+      <c r="C113" s="158"/>
+      <c r="D113" s="158"/>
+    </row>
+    <row r="125" spans="3:9">
       <c r="I125" s="5" t="s">
         <v>107</v>
       </c>
@@ -6056,11 +6159,11 @@
       </c>
       <c r="G26" s="52"/>
       <c r="H26" s="52"/>
-      <c r="K26" s="172" t="s">
+      <c r="K26" s="173" t="s">
         <v>181</v>
       </c>
-      <c r="L26" s="172"/>
-      <c r="M26" s="172"/>
+      <c r="L26" s="173"/>
+      <c r="M26" s="173"/>
     </row>
     <row r="27" spans="1:24" ht="12.9">
       <c r="A27"/>
@@ -6791,26 +6894,26 @@
       </c>
     </row>
     <row r="15" spans="1:10">
-      <c r="B15" s="173" t="s">
+      <c r="B15" s="174" t="s">
         <v>123</v>
       </c>
-      <c r="C15" s="173"/>
-      <c r="D15" s="173"/>
-      <c r="G15" s="173" t="s">
+      <c r="C15" s="174"/>
+      <c r="D15" s="174"/>
+      <c r="G15" s="174" t="s">
         <v>122</v>
       </c>
-      <c r="H15" s="173"/>
-      <c r="I15" s="173"/>
-      <c r="J15" s="173"/>
+      <c r="H15" s="174"/>
+      <c r="I15" s="174"/>
+      <c r="J15" s="174"/>
     </row>
     <row r="17" spans="1:10">
-      <c r="B17" s="174" t="s">
+      <c r="B17" s="175" t="s">
         <v>127</v>
       </c>
-      <c r="C17" s="174" t="s">
+      <c r="C17" s="175" t="s">
         <v>128</v>
       </c>
-      <c r="D17" s="174" t="s">
+      <c r="D17" s="175" t="s">
         <v>129</v>
       </c>
       <c r="G17" s="63" t="s">
@@ -6827,9 +6930,9 @@
       </c>
     </row>
     <row r="18" spans="1:10">
-      <c r="B18" s="174"/>
-      <c r="C18" s="174"/>
-      <c r="D18" s="174"/>
+      <c r="B18" s="175"/>
+      <c r="C18" s="175"/>
+      <c r="D18" s="175"/>
       <c r="F18" t="str">
         <f>H9</f>
         <v>{{YEAR}}</v>

--- a/src/templates/pricing_spreadsheet.xlsx
+++ b/src/templates/pricing_spreadsheet.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3309EA46-4FE8-4715-9DF1-A535F05D8340}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24892" windowHeight="14914" activeTab="1" xr2:uid="{25869D54-3781-4886-8FF9-0A7E0B41E358}"/>
+    <workbookView xWindow="343" yWindow="3317" windowWidth="15514" windowHeight="10740" activeTab="1" xr2:uid="{25869D54-3781-4886-8FF9-0A7E0B41E358}"/>
   </bookViews>
   <sheets>
     <sheet name="Customer Info" sheetId="9" r:id="rId1"/>
